--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T03:51:27Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T03:51:27Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:28:29Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:28:29Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:28:29Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:28:29Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:36:57Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:36:57Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:36:57Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:36:57Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:46:19Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:46:19Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:46:19Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:46:19Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:14Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:33Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:33Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:33Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:33Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:19Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:19Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:19Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:19Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:48Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:48Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:48Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:48Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:42Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:42Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:42Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:42Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:35Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:35Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/master_university_contacts.xlsx
+++ b/workbooks/master_university_contacts.xlsx
@@ -27,8 +27,8 @@
   <dc:title>University Contacts</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:35Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:35Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:57:17Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:57:17Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
